--- a/Team-Data/2013-14/2-20-2013-14.xlsx
+++ b/Team-Data/2013-14/2-20-2013-14.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -739,7 +806,7 @@
         <v>0</v>
       </c>
       <c r="AD2" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE2" t="n">
         <v>16</v>
@@ -751,7 +818,7 @@
         <v>17</v>
       </c>
       <c r="AH2" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI2" t="n">
         <v>15</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>2-20-2013-14</t>
+          <t>2014-02-20</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>-3.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE3" t="n">
         <v>24</v>
@@ -978,7 +1045,7 @@
         <v>23</v>
       </c>
       <c r="AW3" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AX3" t="n">
         <v>15</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>2-20-2013-14</t>
+          <t>2014-02-20</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-2.1</v>
       </c>
       <c r="AD4" t="n">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AE4" t="n">
         <v>16</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>2-20-2013-14</t>
+          <t>2014-02-20</t>
         </is>
       </c>
     </row>
@@ -1285,7 +1352,7 @@
         <v>-1.7</v>
       </c>
       <c r="AD5" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
         <v>16</v>
@@ -1315,7 +1382,7 @@
         <v>28</v>
       </c>
       <c r="AN5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AO5" t="n">
         <v>13</v>
@@ -1324,7 +1391,7 @@
         <v>7</v>
       </c>
       <c r="AQ5" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AR5" t="n">
         <v>28</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>2-20-2013-14</t>
+          <t>2014-02-20</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>0</v>
       </c>
       <c r="AD6" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE6" t="n">
         <v>13</v>
@@ -1521,7 +1588,7 @@
         <v>11</v>
       </c>
       <c r="AV6" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AW6" t="n">
         <v>20</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>2-20-2013-14</t>
+          <t>2014-02-20</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-4.5</v>
       </c>
       <c r="AD7" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE7" t="n">
         <v>21</v>
@@ -1679,7 +1746,7 @@
         <v>21</v>
       </c>
       <c r="AN7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AO7" t="n">
         <v>16</v>
@@ -1688,7 +1755,7 @@
         <v>16</v>
       </c>
       <c r="AQ7" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AR7" t="n">
         <v>3</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>2-20-2013-14</t>
+          <t>2014-02-20</t>
         </is>
       </c>
     </row>
@@ -1831,10 +1898,10 @@
         <v>1.9</v>
       </c>
       <c r="AD8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>2-20-2013-14</t>
+          <t>2014-02-20</t>
         </is>
       </c>
     </row>
@@ -1935,16 +2002,16 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="F9" t="n">
         <v>28</v>
       </c>
       <c r="G9" t="n">
-        <v>0.472</v>
+        <v>0.462</v>
       </c>
       <c r="H9" t="n">
         <v>48.1</v>
@@ -1953,37 +2020,37 @@
         <v>38</v>
       </c>
       <c r="J9" t="n">
-        <v>84.8</v>
+        <v>85</v>
       </c>
       <c r="K9" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L9" t="n">
         <v>8.300000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="N9" t="n">
-        <v>0.358</v>
+        <v>0.357</v>
       </c>
       <c r="O9" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P9" t="n">
         <v>26</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.724</v>
+        <v>0.727</v>
       </c>
       <c r="R9" t="n">
         <v>12.3</v>
       </c>
       <c r="S9" t="n">
-        <v>33.1</v>
+        <v>33.2</v>
       </c>
       <c r="T9" t="n">
-        <v>45.4</v>
+        <v>45.5</v>
       </c>
       <c r="U9" t="n">
         <v>22</v>
@@ -1992,7 +2059,7 @@
         <v>15.5</v>
       </c>
       <c r="W9" t="n">
-        <v>7.1</v>
+        <v>7.2</v>
       </c>
       <c r="X9" t="n">
         <v>5.7</v>
@@ -2001,7 +2068,7 @@
         <v>5.4</v>
       </c>
       <c r="Z9" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="AA9" t="n">
         <v>21.4</v>
@@ -2010,19 +2077,19 @@
         <v>103.1</v>
       </c>
       <c r="AC9" t="n">
-        <v>-1.3</v>
+        <v>-1.5</v>
       </c>
       <c r="AD9" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AE9" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AF9" t="n">
         <v>15</v>
       </c>
       <c r="AG9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AH9" t="n">
         <v>27</v>
@@ -2031,10 +2098,10 @@
         <v>14</v>
       </c>
       <c r="AJ9" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK9" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AL9" t="n">
         <v>9</v>
@@ -2043,16 +2110,16 @@
         <v>9</v>
       </c>
       <c r="AN9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AO9" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AP9" t="n">
         <v>5</v>
       </c>
       <c r="AQ9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR9" t="n">
         <v>5</v>
@@ -2061,7 +2128,7 @@
         <v>8</v>
       </c>
       <c r="AT9" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU9" t="n">
         <v>13</v>
@@ -2070,7 +2137,7 @@
         <v>24</v>
       </c>
       <c r="AW9" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX9" t="n">
         <v>5</v>
@@ -2079,7 +2146,7 @@
         <v>22</v>
       </c>
       <c r="AZ9" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BA9" t="n">
         <v>7</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>2-20-2013-14</t>
+          <t>2014-02-20</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-2.5</v>
       </c>
       <c r="AD10" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AE10" t="n">
         <v>21</v>
@@ -2207,7 +2274,7 @@
         <v>21</v>
       </c>
       <c r="AH10" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI10" t="n">
         <v>7</v>
@@ -2216,7 +2283,7 @@
         <v>4</v>
       </c>
       <c r="AK10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AL10" t="n">
         <v>26</v>
@@ -2255,7 +2322,7 @@
         <v>3</v>
       </c>
       <c r="AX10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AY10" t="n">
         <v>16</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>2-20-2013-14</t>
+          <t>2014-02-20</t>
         </is>
       </c>
     </row>
@@ -2299,28 +2366,28 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E11" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F11" t="n">
         <v>22</v>
       </c>
       <c r="G11" t="n">
-        <v>0.6</v>
+        <v>0.593</v>
       </c>
       <c r="H11" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>38.9</v>
+        <v>39</v>
       </c>
       <c r="J11" t="n">
-        <v>85.09999999999999</v>
+        <v>84.90000000000001</v>
       </c>
       <c r="K11" t="n">
-        <v>0.458</v>
+        <v>0.459</v>
       </c>
       <c r="L11" t="n">
         <v>9.199999999999999</v>
@@ -2329,7 +2396,7 @@
         <v>24.2</v>
       </c>
       <c r="N11" t="n">
-        <v>0.38</v>
+        <v>0.381</v>
       </c>
       <c r="O11" t="n">
         <v>16.4</v>
@@ -2338,7 +2405,7 @@
         <v>22</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.744</v>
+        <v>0.743</v>
       </c>
       <c r="R11" t="n">
         <v>11.2</v>
@@ -2350,7 +2417,7 @@
         <v>45.8</v>
       </c>
       <c r="U11" t="n">
-        <v>22.7</v>
+        <v>22.8</v>
       </c>
       <c r="V11" t="n">
         <v>15.9</v>
@@ -2359,16 +2426,16 @@
         <v>7.9</v>
       </c>
       <c r="X11" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y11" t="n">
         <v>4.4</v>
       </c>
       <c r="Z11" t="n">
-        <v>22</v>
+        <v>21.9</v>
       </c>
       <c r="AA11" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="AB11" t="n">
         <v>103.5</v>
@@ -2377,7 +2444,7 @@
         <v>4.7</v>
       </c>
       <c r="AD11" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
@@ -2389,13 +2456,13 @@
         <v>9</v>
       </c>
       <c r="AH11" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AI11" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AJ11" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK11" t="n">
         <v>8</v>
@@ -2407,19 +2474,19 @@
         <v>7</v>
       </c>
       <c r="AN11" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AP11" t="n">
         <v>20</v>
       </c>
       <c r="AQ11" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AR11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AS11" t="n">
         <v>2</v>
@@ -2437,7 +2504,7 @@
         <v>13</v>
       </c>
       <c r="AX11" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AY11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>2-20-2013-14</t>
+          <t>2014-02-20</t>
         </is>
       </c>
     </row>
@@ -2481,85 +2548,85 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E12" t="n">
         <v>37</v>
       </c>
       <c r="F12" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G12" t="n">
-        <v>0.673</v>
+        <v>0.6850000000000001</v>
       </c>
       <c r="H12" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I12" t="n">
         <v>37.6</v>
       </c>
       <c r="J12" t="n">
-        <v>79.7</v>
+        <v>79.3</v>
       </c>
       <c r="K12" t="n">
-        <v>0.472</v>
+        <v>0.475</v>
       </c>
       <c r="L12" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="M12" t="n">
-        <v>26.1</v>
+        <v>26</v>
       </c>
       <c r="N12" t="n">
-        <v>0.353</v>
+        <v>0.354</v>
       </c>
       <c r="O12" t="n">
-        <v>21.4</v>
+        <v>21.5</v>
       </c>
       <c r="P12" t="n">
-        <v>31.1</v>
+        <v>31.2</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.6889999999999999</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="R12" t="n">
-        <v>11.3</v>
+        <v>11.1</v>
       </c>
       <c r="S12" t="n">
-        <v>34.1</v>
+        <v>34</v>
       </c>
       <c r="T12" t="n">
-        <v>45.4</v>
+        <v>45.1</v>
       </c>
       <c r="U12" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V12" t="n">
         <v>16.2</v>
       </c>
       <c r="W12" t="n">
-        <v>7.4</v>
+        <v>7.5</v>
       </c>
       <c r="X12" t="n">
         <v>5.8</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="Z12" t="n">
-        <v>20.1</v>
+        <v>20</v>
       </c>
       <c r="AA12" t="n">
         <v>24.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>105.9</v>
+        <v>106</v>
       </c>
       <c r="AC12" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="AD12" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="AE12" t="n">
         <v>5</v>
@@ -2571,7 +2638,7 @@
         <v>5</v>
       </c>
       <c r="AH12" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AI12" t="n">
         <v>16</v>
@@ -2601,13 +2668,13 @@
         <v>29</v>
       </c>
       <c r="AR12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AS12" t="n">
         <v>4</v>
       </c>
       <c r="AT12" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU12" t="n">
         <v>22</v>
@@ -2625,7 +2692,7 @@
         <v>23</v>
       </c>
       <c r="AZ12" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA12" t="n">
         <v>1</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>2-20-2013-14</t>
+          <t>2014-02-20</t>
         </is>
       </c>
     </row>
@@ -2741,19 +2808,19 @@
         <v>7.8</v>
       </c>
       <c r="AD13" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AE13" t="n">
         <v>2</v>
       </c>
       <c r="AF13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG13" t="n">
         <v>2</v>
       </c>
       <c r="AH13" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AI13" t="n">
         <v>21</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>2-20-2013-14</t>
+          <t>2014-02-20</t>
         </is>
       </c>
     </row>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>2-20-2013-14</t>
+          <t>2014-02-20</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-5.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3171,7 +3238,7 @@
         <v>14</v>
       </c>
       <c r="AZ15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BA15" t="n">
         <v>27</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>2-20-2013-14</t>
+          <t>2014-02-20</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>0.3</v>
       </c>
       <c r="AD16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE16" t="n">
         <v>11</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>2-20-2013-14</t>
+          <t>2014-02-20</t>
         </is>
       </c>
     </row>
@@ -3391,22 +3458,22 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E17" t="n">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="F17" t="n">
         <v>14</v>
       </c>
       <c r="G17" t="n">
-        <v>0.736</v>
+        <v>0.731</v>
       </c>
       <c r="H17" t="n">
         <v>48.5</v>
       </c>
       <c r="I17" t="n">
-        <v>39.1</v>
+        <v>39</v>
       </c>
       <c r="J17" t="n">
         <v>76.7</v>
@@ -3418,16 +3485,16 @@
         <v>8.1</v>
       </c>
       <c r="M17" t="n">
-        <v>21.9</v>
+        <v>22</v>
       </c>
       <c r="N17" t="n">
-        <v>0.368</v>
+        <v>0.37</v>
       </c>
       <c r="O17" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="P17" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="Q17" t="n">
         <v>0.758</v>
@@ -3436,19 +3503,19 @@
         <v>7.3</v>
       </c>
       <c r="S17" t="n">
-        <v>29.4</v>
+        <v>29.3</v>
       </c>
       <c r="T17" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="U17" t="n">
         <v>23.5</v>
       </c>
       <c r="V17" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W17" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X17" t="n">
         <v>4.3</v>
@@ -3460,16 +3527,16 @@
         <v>20.2</v>
       </c>
       <c r="AA17" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AB17" t="n">
         <v>104.4</v>
       </c>
       <c r="AC17" t="n">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="AD17" t="n">
-        <v>22</v>
+        <v>28</v>
       </c>
       <c r="AE17" t="n">
         <v>4</v>
@@ -3481,10 +3548,10 @@
         <v>3</v>
       </c>
       <c r="AH17" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AI17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AJ17" t="n">
         <v>30</v>
@@ -3496,7 +3563,7 @@
         <v>11</v>
       </c>
       <c r="AM17" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AN17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>2-20-2013-14</t>
+          <t>2014-02-20</t>
         </is>
       </c>
     </row>
@@ -3573,19 +3640,19 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E18" t="n">
         <v>10</v>
       </c>
       <c r="F18" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="G18" t="n">
-        <v>0.185</v>
+        <v>0.189</v>
       </c>
       <c r="H18" t="n">
-        <v>48.6</v>
+        <v>48.7</v>
       </c>
       <c r="I18" t="n">
         <v>35</v>
@@ -3597,13 +3664,13 @@
         <v>0.423</v>
       </c>
       <c r="L18" t="n">
-        <v>7.2</v>
+        <v>7.3</v>
       </c>
       <c r="M18" t="n">
         <v>20.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0.351</v>
+        <v>0.354</v>
       </c>
       <c r="O18" t="n">
         <v>15.3</v>
@@ -3618,22 +3685,22 @@
         <v>11.5</v>
       </c>
       <c r="S18" t="n">
-        <v>29.6</v>
+        <v>29.7</v>
       </c>
       <c r="T18" t="n">
-        <v>41.1</v>
+        <v>41.2</v>
       </c>
       <c r="U18" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="V18" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W18" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="X18" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Y18" t="n">
         <v>5.3</v>
@@ -3651,7 +3718,7 @@
         <v>-9.300000000000001</v>
       </c>
       <c r="AD18" t="n">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="AE18" t="n">
         <v>30</v>
@@ -3696,7 +3763,7 @@
         <v>14</v>
       </c>
       <c r="AS18" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AT18" t="n">
         <v>25</v>
@@ -3705,10 +3772,10 @@
         <v>18</v>
       </c>
       <c r="AV18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AW18" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX18" t="n">
         <v>7</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>2-20-2013-14</t>
+          <t>2014-02-20</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>3.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AE19" t="n">
         <v>14</v>
@@ -3860,7 +3927,7 @@
         <v>16</v>
       </c>
       <c r="AM19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AN19" t="n">
         <v>26</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>2-20-2013-14</t>
+          <t>2014-02-20</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-1.7</v>
       </c>
       <c r="AD20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE20" t="n">
         <v>20</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>2-20-2013-14</t>
+          <t>2014-02-20</t>
         </is>
       </c>
     </row>
@@ -4197,7 +4264,7 @@
         <v>-1.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AE21" t="n">
         <v>23</v>
@@ -4242,7 +4309,7 @@
         <v>19</v>
       </c>
       <c r="AS21" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AT21" t="n">
         <v>27</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>2-20-2013-14</t>
+          <t>2014-02-20</t>
         </is>
       </c>
     </row>
@@ -4301,67 +4368,67 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E22" t="n">
         <v>43</v>
       </c>
       <c r="F22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="G22" t="n">
-        <v>0.768</v>
+        <v>0.782</v>
       </c>
       <c r="H22" t="n">
         <v>48.2</v>
       </c>
       <c r="I22" t="n">
-        <v>38.9</v>
+        <v>39.1</v>
       </c>
       <c r="J22" t="n">
-        <v>82.09999999999999</v>
+        <v>82.3</v>
       </c>
       <c r="K22" t="n">
-        <v>0.474</v>
+        <v>0.475</v>
       </c>
       <c r="L22" t="n">
-        <v>7.3</v>
+        <v>7.4</v>
       </c>
       <c r="M22" t="n">
         <v>20.6</v>
       </c>
       <c r="N22" t="n">
-        <v>0.354</v>
+        <v>0.358</v>
       </c>
       <c r="O22" t="n">
         <v>19.4</v>
       </c>
       <c r="P22" t="n">
-        <v>24.2</v>
+        <v>24.1</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.803</v>
+        <v>0.804</v>
       </c>
       <c r="R22" t="n">
         <v>11</v>
       </c>
       <c r="S22" t="n">
-        <v>34.3</v>
+        <v>34.4</v>
       </c>
       <c r="T22" t="n">
-        <v>45.3</v>
+        <v>45.4</v>
       </c>
       <c r="U22" t="n">
-        <v>21.5</v>
+        <v>21.6</v>
       </c>
       <c r="V22" t="n">
-        <v>15.8</v>
+        <v>15.7</v>
       </c>
       <c r="W22" t="n">
         <v>8.199999999999999</v>
       </c>
       <c r="X22" t="n">
-        <v>6.1</v>
+        <v>6.2</v>
       </c>
       <c r="Y22" t="n">
         <v>3.8</v>
@@ -4373,13 +4440,13 @@
         <v>20</v>
       </c>
       <c r="AB22" t="n">
-        <v>104.6</v>
+        <v>105</v>
       </c>
       <c r="AC22" t="n">
-        <v>6.9</v>
+        <v>7.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4394,7 +4461,7 @@
         <v>26</v>
       </c>
       <c r="AI22" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AJ22" t="n">
         <v>20</v>
@@ -4409,7 +4476,7 @@
         <v>18</v>
       </c>
       <c r="AN22" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AO22" t="n">
         <v>5</v>
@@ -4427,13 +4494,13 @@
         <v>3</v>
       </c>
       <c r="AT22" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AU22" t="n">
         <v>14</v>
       </c>
       <c r="AV22" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AW22" t="n">
         <v>11</v>
@@ -4451,7 +4518,7 @@
         <v>19</v>
       </c>
       <c r="BB22" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC22" t="n">
         <v>2</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>2-20-2013-14</t>
+          <t>2014-02-20</t>
         </is>
       </c>
     </row>
@@ -4594,7 +4661,7 @@
         <v>22</v>
       </c>
       <c r="AO23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AP23" t="n">
         <v>22</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>2-20-2013-14</t>
+          <t>2014-02-20</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-10.5</v>
       </c>
       <c r="AD24" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE24" t="n">
         <v>29</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>2-20-2013-14</t>
+          <t>2014-02-20</t>
         </is>
       </c>
     </row>
@@ -4925,10 +4992,10 @@
         <v>3.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE25" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF25" t="n">
         <v>8</v>
@@ -4937,7 +5004,7 @@
         <v>8</v>
       </c>
       <c r="AH25" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AI25" t="n">
         <v>9</v>
@@ -4997,7 +5064,7 @@
         <v>8</v>
       </c>
       <c r="BB25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>2-20-2013-14</t>
+          <t>2014-02-20</t>
         </is>
       </c>
     </row>
@@ -5107,13 +5174,13 @@
         <v>4</v>
       </c>
       <c r="AD26" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AE26" t="n">
         <v>7</v>
       </c>
       <c r="AF26" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG26" t="n">
         <v>6</v>
@@ -5137,7 +5204,7 @@
         <v>5</v>
       </c>
       <c r="AN26" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO26" t="n">
         <v>6</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>2-20-2013-14</t>
+          <t>2014-02-20</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-2.4</v>
       </c>
       <c r="AD27" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AE27" t="n">
         <v>26</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>2-20-2013-14</t>
+          <t>2014-02-20</t>
         </is>
       </c>
     </row>
@@ -5471,7 +5538,7 @@
         <v>6.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE28" t="n">
         <v>3</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>2-20-2013-14</t>
+          <t>2014-02-20</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>2.8</v>
       </c>
       <c r="AD29" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AE29" t="n">
         <v>12</v>
@@ -5686,7 +5753,7 @@
         <v>13</v>
       </c>
       <c r="AO29" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AP29" t="n">
         <v>9</v>
@@ -5719,7 +5786,7 @@
         <v>13</v>
       </c>
       <c r="AZ29" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="BA29" t="n">
         <v>5</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>2-20-2013-14</t>
+          <t>2014-02-20</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>-5.9</v>
       </c>
       <c r="AD30" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AE30" t="n">
         <v>24</v>
@@ -5892,7 +5959,7 @@
         <v>14</v>
       </c>
       <c r="AW30" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX30" t="n">
         <v>19</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>2-20-2013-14</t>
+          <t>2014-02-20</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>0</v>
       </c>
       <c r="AD31" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AE31" t="n">
         <v>14</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>2-20-2013-14</t>
+          <t>2014-02-20</t>
         </is>
       </c>
     </row>
